--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/LOUISIANA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/LOUISIANA_2018.xlsx
@@ -3642,7 +3642,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C183">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C431">
